--- a/cristian/tabla_materiales_pic32_pinguino.xlsx
+++ b/cristian/tabla_materiales_pic32_pinguino.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Crist\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B994D88F-8D91-4E1F-9BEA-C608EA8870BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4975317-5584-4428-B9F5-479092DE6934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,218 +18,6 @@
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="20">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="6"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="7"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="10"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="11"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="12"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="13"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="14"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="15"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="16"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="17"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="18"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="19"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="20">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-    <bk>
-      <rc t="1" v="1"/>
-    </bk>
-    <bk>
-      <rc t="1" v="2"/>
-    </bk>
-    <bk>
-      <rc t="1" v="3"/>
-    </bk>
-    <bk>
-      <rc t="1" v="4"/>
-    </bk>
-    <bk>
-      <rc t="1" v="5"/>
-    </bk>
-    <bk>
-      <rc t="1" v="6"/>
-    </bk>
-    <bk>
-      <rc t="1" v="7"/>
-    </bk>
-    <bk>
-      <rc t="1" v="8"/>
-    </bk>
-    <bk>
-      <rc t="1" v="9"/>
-    </bk>
-    <bk>
-      <rc t="1" v="10"/>
-    </bk>
-    <bk>
-      <rc t="1" v="11"/>
-    </bk>
-    <bk>
-      <rc t="1" v="12"/>
-    </bk>
-    <bk>
-      <rc t="1" v="13"/>
-    </bk>
-    <bk>
-      <rc t="1" v="14"/>
-    </bk>
-    <bk>
-      <rc t="1" v="15"/>
-    </bk>
-    <bk>
-      <rc t="1" v="16"/>
-    </bk>
-    <bk>
-      <rc t="1" v="17"/>
-    </bk>
-    <bk>
-      <rc t="1" v="18"/>
-    </bk>
-    <bk>
-      <rc t="1" v="19"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -593,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -618,9 +406,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -888,140 +673,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="20">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>1</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>2</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>3</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>4</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>5</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>6</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>7</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>8</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>9</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>10</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>11</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>12</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>13</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>14</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>15</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>16</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>17</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>18</v>
-    <v>5</v>
-  </rv>
-  <rv s="0">
-    <v>19</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
 <file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
@@ -1319,9 +970,7 @@
       <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="2" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D7" s="2"/>
       <c r="E7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1336,9 +985,7 @@
       <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="2" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
@@ -1353,9 +1000,7 @@
       <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="2" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
@@ -1370,9 +1015,7 @@
       <c r="C10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="2" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D10" s="2"/>
       <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
@@ -1387,9 +1030,7 @@
       <c r="C11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="2" t="e" vm="5">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
@@ -1404,9 +1045,7 @@
       <c r="C12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="2" t="e" vm="6">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D12" s="2"/>
       <c r="E12" s="1" t="s">
         <v>33</v>
       </c>
@@ -1421,9 +1060,7 @@
       <c r="C13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="2" t="e" vm="7">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1438,9 +1075,7 @@
       <c r="C14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="2" t="e" vm="8">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D14" s="2"/>
       <c r="E14" s="1" t="s">
         <v>40</v>
       </c>
@@ -1455,9 +1090,7 @@
       <c r="C15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D15" s="2" t="e" vm="9">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="1" t="s">
         <v>43</v>
       </c>
@@ -1472,9 +1105,7 @@
       <c r="C16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="2" t="e" vm="10">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D16" s="2"/>
       <c r="E16" s="1" t="s">
         <v>46</v>
       </c>
@@ -1489,9 +1120,7 @@
       <c r="C17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="2" t="e" vm="11">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D17" s="2"/>
       <c r="E17" s="1" t="s">
         <v>48</v>
       </c>
@@ -1506,9 +1135,7 @@
       <c r="C18" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="9" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D18" s="2"/>
       <c r="E18" s="1" t="s">
         <v>49</v>
       </c>
@@ -1523,9 +1150,7 @@
       <c r="C19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="2" t="e" vm="13">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D19" s="2"/>
       <c r="E19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1540,9 +1165,7 @@
       <c r="C20" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="2" t="e" vm="14">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D20" s="2"/>
       <c r="E20" s="1" t="s">
         <v>52</v>
       </c>
@@ -1557,9 +1180,7 @@
       <c r="C21" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="2" t="e" vm="14">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D21" s="2"/>
       <c r="E21" s="1" t="s">
         <v>52</v>
       </c>
@@ -1574,9 +1195,7 @@
       <c r="C22" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="2" t="e" vm="15">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D22" s="2"/>
       <c r="E22" s="1" t="s">
         <v>54</v>
       </c>
@@ -1591,9 +1210,7 @@
       <c r="C23" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="2" t="e" vm="16">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D23" s="2"/>
       <c r="E23" s="1" t="s">
         <v>52</v>
       </c>
@@ -1608,9 +1225,7 @@
       <c r="C24" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="2" t="e" vm="17">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="1" t="s">
         <v>58</v>
       </c>
@@ -1625,9 +1240,7 @@
       <c r="C25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="2" t="e" vm="18">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D25" s="2"/>
       <c r="E25" s="1" t="s">
         <v>60</v>
       </c>
@@ -1642,9 +1255,7 @@
       <c r="C26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="2" t="e" vm="19">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D26" s="2"/>
       <c r="E26" s="1" t="s">
         <v>61</v>
       </c>
@@ -1659,9 +1270,7 @@
       <c r="C27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="2" t="e" vm="20">
-        <v>#VALUE!</v>
-      </c>
+      <c r="D27" s="2"/>
       <c r="E27" s="1" t="s">
         <v>62</v>
       </c>
